--- a/docs/Login-Instruktur-MK.xlsx
+++ b/docs/Login-Instruktur-MK.xlsx
@@ -551,7 +551,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -600,7 +599,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>annaGGMK</t>
+          <t>annadesi</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -630,7 +629,7 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>asriGGMK</t>
+          <t>asrigelv</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -660,7 +659,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>gressyaMK</t>
+          <t>gressya</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -690,7 +689,7 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>linaMKUNTAR</t>
+          <t>linalind</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
@@ -720,7 +719,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>silvester</t>
+          <t>silvest</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
